--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487103_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487103_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.189500000000001</v>
+        <v>7.4494</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9604</v>
+        <v>5.4786</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2291</v>
+        <v>1.9709</v>
       </c>
       <c r="G2" t="n">
         <v>6.6476</v>
@@ -610,13 +610,13 @@
         <v>3.4741</v>
       </c>
       <c r="S2" t="n">
-        <v>4.0207</v>
+        <v>2.2807</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0048</v>
+        <v>0.5229</v>
       </c>
       <c r="U2" t="n">
-        <v>3.016</v>
+        <v>1.7578</v>
       </c>
       <c r="V2" t="n">
         <v>-0.8999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. CARPINTERO REVILLA</t>
+          <t>F. AMBROSONI ÁLVAREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9156</v>
+        <v>4.5568</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2535</v>
+        <v>1.9262</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6622</v>
+        <v>2.6306</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8303</v>
+        <v>4.3994</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5168</v>
+        <v>2.3909</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6865</v>
+        <v>2.0086</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5768</v>
+        <v>5.22</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0166</v>
+        <v>2.7787</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4398</v>
+        <v>2.4413</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.8205</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5002</v>
+        <v>-0.3878</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2467</v>
+        <v>-0.4327</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9301</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>-4.0532</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8951</v>
+        <v>2.3161</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0973</v>
+        <v>0.3384</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9698</v>
+        <v>-0.1404</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1275</v>
+        <v>0.4788</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9421</v>
+        <v>1.5561</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3281</v>
+        <v>0.8999</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.614</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. AMBROSONI ÁLVAREZ</t>
+          <t>E. CARPINTERO REVILLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7022</v>
+        <v>3.9876</v>
       </c>
       <c r="E4" t="n">
-        <v>1.366</v>
+        <v>1.8703</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3362</v>
+        <v>2.1172</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3994</v>
+        <v>1.8303</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3909</v>
+        <v>3.5168</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0086</v>
+        <v>-1.6865</v>
       </c>
       <c r="J4" t="n">
-        <v>5.22</v>
+        <v>2.5768</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7787</v>
+        <v>3.0166</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4413</v>
+        <v>-0.4398</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8205</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3878</v>
+        <v>0.5002</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4327</v>
+        <v>-1.2467</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.0532</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3161</v>
+        <v>2.8951</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5162</v>
+        <v>1.1693</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7006</v>
+        <v>0.5867</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1844</v>
+        <v>0.5826</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5561</v>
+        <v>-0.9421</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8999</v>
+        <v>-0.3281</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6562</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4582</v>
+        <v>1.4642</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4275</v>
+        <v>0.728</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0307</v>
+        <v>0.7362</v>
       </c>
       <c r="G5" t="n">
         <v>0.8853</v>
@@ -844,13 +844,13 @@
         <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1024</v>
+        <v>0.1084</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3569</v>
+        <v>-0.0565</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4594</v>
+        <v>0.1649</v>
       </c>
       <c r="V5" t="n">
         <v>0.08450000000000001</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8545</v>
+        <v>1.1014</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2897</v>
+        <v>-2.2303</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1443</v>
+        <v>3.3316</v>
       </c>
       <c r="G6" t="n">
         <v>0.8875999999999999</v>
@@ -922,13 +922,13 @@
         <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2611</v>
+        <v>-0.0142</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0462</v>
+        <v>0.0132</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2148</v>
+        <v>-0.0275</v>
       </c>
       <c r="V6" t="n">
         <v>0.614</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4111</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2401</v>
+        <v>1.7408</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>0.9675</v>
@@ -1000,13 +1000,13 @@
         <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6716</v>
+        <v>1.1098</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0462</v>
+        <v>0.4545</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7178</v>
+        <v>0.6553</v>
       </c>
       <c r="V7" t="n">
         <v>-1.228</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. HERNANDEZ HERNANDEZ</t>
+          <t>J. PATERNINA ARBIDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4554</v>
+        <v>-0.0467</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8718</v>
+        <v>0.1246</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3271</v>
+        <v>-0.1714</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.32</v>
+        <v>-0.8115</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2029</v>
+        <v>-0.1717</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1171</v>
+        <v>-0.6398</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1821</v>
+        <v>0.1028</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0193</v>
+        <v>0.0621</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1628</v>
+        <v>0.0407</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5021</v>
+        <v>-0.9143</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2222</v>
+        <v>-0.2338</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2799</v>
+        <v>-0.6805</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0.386</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0926</v>
+        <v>0.3787</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5619</v>
+        <v>0.0218</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.3569</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PATERNINA ARBIDE</t>
+          <t>O. HERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-1.084</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1352</v>
+        <v>0.4305</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3855</v>
+        <v>-1.5145</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8115</v>
+        <v>-0.32</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1717</v>
+        <v>-0.2029</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6398</v>
+        <v>-0.1171</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1028</v>
+        <v>1.1821</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0621</v>
+        <v>1.0193</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0407</v>
+        <v>0.1628</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9143</v>
+        <v>-1.5021</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2338</v>
+        <v>-1.2222</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6805</v>
+        <v>-0.2799</v>
       </c>
       <c r="P10" t="n">
-        <v>0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R10" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.464</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.238</v>
+        <v>0.1207</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1428</v>
+        <v>0.3434</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4767</v>
+        <v>-1.5602</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7956</v>
+        <v>-2.5751</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3189</v>
+        <v>1.0149</v>
       </c>
       <c r="G11" t="n">
         <v>0.3636</v>
@@ -1312,13 +1312,13 @@
         <v>3.0881</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8679</v>
+        <v>0.0486</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4277</v>
+        <v>-0.2072</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4402</v>
+        <v>0.2558</v>
       </c>
       <c r="V11" t="n">
         <v>-0.0422</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>16.2118</v>
+        <v>16.8513</v>
       </c>
       <c r="E12" t="n">
-        <v>6.8988</v>
+        <v>7.4936</v>
       </c>
       <c r="F12" t="n">
-        <v>9.313199999999998</v>
+        <v>9.357399999999998</v>
       </c>
       <c r="G12" t="n">
         <v>15.2504</v>
@@ -1360,7 +1360,7 @@
         <v>11.1162</v>
       </c>
       <c r="I12" t="n">
-        <v>4.134199999999999</v>
+        <v>4.134200000000001</v>
       </c>
       <c r="J12" t="n">
         <v>21.9219</v>
@@ -1369,10 +1369,10 @@
         <v>13.5569</v>
       </c>
       <c r="L12" t="n">
-        <v>8.364999999999998</v>
+        <v>8.365</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.671399999999999</v>
+        <v>-6.6714</v>
       </c>
       <c r="N12" t="n">
         <v>-2.4407</v>
@@ -1390,22 +1390,22 @@
         <v>17.3706</v>
       </c>
       <c r="S12" t="n">
-        <v>4.977200000000001</v>
+        <v>5.616700000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7208999999999997</v>
+        <v>1.3157</v>
       </c>
       <c r="U12" t="n">
-        <v>4.256600000000001</v>
+        <v>4.301</v>
       </c>
       <c r="V12" t="n">
         <v>-2.0856</v>
       </c>
       <c r="W12" t="n">
-        <v>3.5572</v>
+        <v>3.557199999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.6428</v>
+        <v>-5.642799999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5885</v>
+        <v>1.3753</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1883</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4002</v>
+        <v>0.5876</v>
       </c>
       <c r="G13" t="n">
         <v>1.3459</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5294</v>
+        <v>-0.7426</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0132</v>
+        <v>-0.3873</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5427</v>
+        <v>-0.3553</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8235</v>
+        <v>0.9435</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5475</v>
+        <v>0.7478</v>
       </c>
       <c r="F14" t="n">
-        <v>0.276</v>
+        <v>0.1957</v>
       </c>
       <c r="G14" t="n">
         <v>-0.1257</v>
@@ -1546,13 +1546,13 @@
         <v>0.386</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0086</v>
+        <v>0.1114</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0449</v>
+        <v>0.1553</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0363</v>
+        <v>-0.044</v>
       </c>
       <c r="V14" t="n">
         <v>0.5717</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>S. MARTINEZ ORTIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3764</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4567</v>
+        <v>0.023</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0802</v>
+        <v>0.8696</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.2848</v>
+        <v>-0.7296</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2401</v>
+        <v>-2.1134</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0446</v>
+        <v>1.3838</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2197</v>
+        <v>0.4518</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3243</v>
+        <v>-0.8177</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8954</v>
+        <v>1.2695</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.5044</v>
+        <v>-1.1814</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.5644</v>
+        <v>-1.2956</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.94</v>
+        <v>0.1142</v>
       </c>
       <c r="P15" t="n">
-        <v>2.8951</v>
+        <v>-0.193</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>3.8602</v>
+        <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7634</v>
+        <v>-0.0268</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6133</v>
+        <v>-0.3407</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1501</v>
+        <v>0.3139</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5295</v>
+        <v>1.842</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8154</v>
+        <v>1.842</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MARTINEZ ORTIZ</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.031</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.678</v>
+        <v>1.3565</v>
       </c>
       <c r="F16" t="n">
-        <v>0.709</v>
+        <v>-1.2676</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7296</v>
+        <v>-2.2848</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.1134</v>
+        <v>-1.2401</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3838</v>
+        <v>-1.0446</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4518</v>
+        <v>2.2197</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8177</v>
+        <v>1.3243</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2695</v>
+        <v>0.8954</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1814</v>
+        <v>-4.5044</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2956</v>
+        <v>-2.5644</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1142</v>
+        <v>-1.94</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.193</v>
+        <v>2.8951</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7371</v>
+        <v>3.8602</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8884</v>
+        <v>-1.051</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0417</v>
+        <v>-0.7135</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1533</v>
+        <v>-0.3375</v>
       </c>
       <c r="V16" t="n">
-        <v>1.842</v>
+        <v>0.5295</v>
       </c>
       <c r="W16" t="n">
-        <v>1.842</v>
+        <v>0.8154</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4317</v>
+        <v>-1.362</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.671</v>
+        <v>-1.6617</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2393</v>
+        <v>0.2997</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.5797</v>
+        <v>0.2574</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8475</v>
+        <v>-0.2588</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7322</v>
+        <v>0.5162</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.7574</v>
+        <v>1.9793</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08260000000000001</v>
+        <v>1.3038</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.84</v>
+        <v>0.6755</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8222</v>
+        <v>-1.7219</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.93</v>
+        <v>-1.5627</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1078</v>
+        <v>-0.1592</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>-0.965</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R17" t="n">
         <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2637</v>
+        <v>-0.3262</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1745</v>
+        <v>-0.4177</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0892</v>
+        <v>0.0915</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8842</v>
+        <v>-0.3281</v>
       </c>
       <c r="W17" t="n">
-        <v>1.842</v>
+        <v>-0.3281</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6287</v>
+        <v>-1.8591</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0622</v>
+        <v>-2.0716</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4335</v>
+        <v>0.2125</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2574</v>
+        <v>-3.5797</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2588</v>
+        <v>-1.8475</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5162</v>
+        <v>-1.7322</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9793</v>
+        <v>-1.7574</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3038</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6755</v>
+        <v>-1.84</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7219</v>
+        <v>-1.8222</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5627</v>
+        <v>-1.93</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1592</v>
+        <v>0.1078</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.965</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
         <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5929</v>
+        <v>-0.1636</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8183</v>
+        <v>-0.226</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2254</v>
+        <v>0.0624</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3281</v>
+        <v>1.8842</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3281</v>
+        <v>1.842</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="19">
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2849</v>
+        <v>-2.1847</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1808</v>
+        <v>-1.0807</v>
       </c>
       <c r="F19" t="n">
         <v>-1.1041</v>
@@ -1936,10 +1936,10 @@
         <v>2.5091</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8474</v>
+        <v>-0.7472</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8645</v>
+        <v>-0.7644</v>
       </c>
       <c r="U19" t="n">
         <v>0.0172</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2911</v>
+        <v>-2.2108</v>
       </c>
       <c r="E20" t="n">
         <v>-0.8822</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4088</v>
+        <v>-1.3285</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0326</v>
@@ -2014,13 +2014,13 @@
         <v>0.386</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6445</v>
+        <v>-0.5642</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2974</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.347</v>
+        <v>-0.2667</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2123</v>
+        <v>-3.9783</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.947</v>
+        <v>-1.8468</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2653</v>
+        <v>-2.1315</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5888</v>
@@ -2170,13 +2170,13 @@
         <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8467</v>
+        <v>-0.6127</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8328</v>
+        <v>-0.7327</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0139</v>
+        <v>0.12</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1278</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4926</v>
+        <v>-5.2273</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9465</v>
+        <v>-4.5473</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5461</v>
+        <v>-0.68</v>
       </c>
       <c r="G23" t="n">
         <v>-5.5022</v>
@@ -2248,13 +2248,13 @@
         <v>3.0881</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4885</v>
+        <v>-0.2462</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3068</v>
+        <v>-0.2941</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1817</v>
+        <v>0.0479</v>
       </c>
       <c r="V23" t="n">
         <v>0.3281</v>
@@ -2284,10 +2284,10 @@
         <v>-16.212</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.313000000000001</v>
+        <v>-9.312999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.8987</v>
+        <v>-6.8988</v>
       </c>
       <c r="G24" t="n">
         <v>-15.2505</v>
@@ -2329,10 +2329,10 @@
         <v>-4.9772</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.2564</v>
+        <v>-4.2565</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7208</v>
+        <v>-0.7207999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>2.085599999999999</v>
